--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.15385335246257</v>
+        <v>3.925001169775168</v>
       </c>
       <c r="D2" t="n">
-        <v>23.69463950017143</v>
+        <v>3.850378918777858</v>
       </c>
       <c r="E2" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F2" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.99965743099671</v>
+        <v>8.774944332536966</v>
       </c>
       <c r="D3" t="n">
-        <v>53.35261775543506</v>
+        <v>8.669800385258197</v>
       </c>
       <c r="E3" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F3" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.38571601349219</v>
+        <v>6.88767885219248</v>
       </c>
       <c r="D4" t="n">
-        <v>42.06704760073075</v>
+        <v>6.835895235118747</v>
       </c>
       <c r="E4" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F4" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.72435364989712</v>
+        <v>6.780207468108282</v>
       </c>
       <c r="D5" t="n">
-        <v>41.59060494591275</v>
+        <v>6.758473303710822</v>
       </c>
       <c r="E5" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F5" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.42351340662578</v>
+        <v>2.831320928576689</v>
       </c>
       <c r="D6" t="n">
-        <v>18.67899430075968</v>
+        <v>3.035336573873447</v>
       </c>
       <c r="E6" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F6" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.08982247182004</v>
+        <v>6.677096151670756</v>
       </c>
       <c r="D7" t="n">
-        <v>41.17683849009255</v>
+        <v>6.69123625464004</v>
       </c>
       <c r="E7" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F7" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.06908579947124</v>
+        <v>4.561226442414077</v>
       </c>
       <c r="D8" t="n">
-        <v>28.77664222724115</v>
+        <v>4.676204361926686</v>
       </c>
       <c r="E8" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F8" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61271541584583</v>
+        <v>5.299566255074947</v>
       </c>
       <c r="D9" t="n">
-        <v>33.94563722932343</v>
+        <v>5.516166049765058</v>
       </c>
       <c r="E9" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F9" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.81198381875788</v>
+        <v>6.631947370548156</v>
       </c>
       <c r="D10" t="n">
-        <v>32.2453910010337</v>
+        <v>5.239876037667976</v>
       </c>
       <c r="E10" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F10" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.87223526374891</v>
+        <v>5.666738230359197</v>
       </c>
       <c r="D11" t="n">
-        <v>23.59110897469731</v>
+        <v>3.833555208388313</v>
       </c>
       <c r="E11" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F11" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>30.24781323726858</v>
+        <v>4.915269651056145</v>
       </c>
       <c r="D12" t="n">
-        <v>26.78685543516767</v>
+        <v>4.352864008214746</v>
       </c>
       <c r="E12" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F12" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.8627556080293</v>
+        <v>3.390197786304761</v>
       </c>
       <c r="D13" t="n">
-        <v>10.27732061174778</v>
+        <v>1.670064599409014</v>
       </c>
       <c r="E13" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F13" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>23.44122759953315</v>
+        <v>3.809199484924136</v>
       </c>
       <c r="D14" t="n">
-        <v>23.60444363906445</v>
+        <v>3.835722091347972</v>
       </c>
       <c r="E14" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F14" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>27.04301877942105</v>
+        <v>4.39449055165592</v>
       </c>
       <c r="D15" t="n">
-        <v>26.65371915862496</v>
+        <v>4.331229363276555</v>
       </c>
       <c r="E15" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F15" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>6.30697812573827</v>
+        <v>1.024883945432469</v>
       </c>
       <c r="D16" t="n">
-        <v>6.604647788716349</v>
+        <v>1.073255265666407</v>
       </c>
       <c r="E16" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F16" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>5.3579081619808</v>
+        <v>0.8706600763218801</v>
       </c>
       <c r="D17" t="n">
-        <v>4.965925133808934</v>
+        <v>0.8069628342439518</v>
       </c>
       <c r="E17" t="n">
-        <v>12.82458332043516</v>
+        <v>2.083994789570713</v>
       </c>
       <c r="F17" t="n">
-        <v>12.98219235381658</v>
+        <v>2.109606257495194</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
